--- a/Result/profitability/3152.xlsx
+++ b/Result/profitability/3152.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.24</v>
       </c>
       <c r="M2" t="n">
-        <v>1.8825</v>
+        <v>1.94</v>
       </c>
       <c r="N2" t="n">
-        <v>44.4025</v>
+        <v>44.35375000000001</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>1.75</v>
       </c>
       <c r="M3" t="n">
-        <v>1.9225</v>
+        <v>1.96125</v>
       </c>
       <c r="N3" t="n">
-        <v>45.22375</v>
+        <v>44.965</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
@@ -798,7 +798,7 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1.7</v>
       </c>
       <c r="M4" t="n">
-        <v>1.9375</v>
+        <v>1.99125</v>
       </c>
       <c r="N4" t="n">
-        <v>45.78875</v>
+        <v>45.5825</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>1.1</v>
       </c>
       <c r="M5" t="n">
-        <v>1.8925</v>
+        <v>1.425</v>
       </c>
       <c r="N5" t="n">
-        <v>45.51625</v>
+        <v>45.46</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.72</v>
       </c>
       <c r="M6" t="n">
-        <v>1.27875</v>
+        <v>1.37375</v>
       </c>
       <c r="N6" t="n">
-        <v>44.705</v>
+        <v>45.03</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.51</v>
       </c>
       <c r="M7" t="n">
-        <v>1.32625</v>
+        <v>1.4125</v>
       </c>
       <c r="N7" t="n">
-        <v>46.13</v>
+        <v>45.965</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>1.83</v>
       </c>
       <c r="M8" t="n">
-        <v>1.405</v>
+        <v>1.4675</v>
       </c>
       <c r="N8" t="n">
-        <v>47.17375</v>
+        <v>46.87</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1403,7 +1403,7 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
@@ -1412,7 +1412,7 @@
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3152</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>406</v>
+      </c>
+      <c r="D75" t="n">
+        <v>233</v>
+      </c>
+      <c r="E75" t="n">
+        <v>174</v>
+      </c>
+      <c r="F75" t="n">
+        <v>42.71</v>
+      </c>
+      <c r="G75" t="n">
+        <v>114</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>28.11%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>10</v>
+      </c>
+      <c r="J75" t="n">
+        <v>124</v>
+      </c>
+      <c r="K75" t="n">
+        <v>96</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.96375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>43.42375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.3597122302158273</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.43</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.05383252104563574</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-3.74</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.6642984014209592</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.4499999999999957</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.01042632066728444</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
